--- a/BVSimulationFiles/73.xlsx
+++ b/BVSimulationFiles/73.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0009601226993865032</v>
+        <v>0.001920245398773006</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009677106877623507</v>
+        <v>0.001935421375524701</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0009752986761381984</v>
+        <v>0.001950597352276397</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009828866645140461</v>
+        <v>0.001965773329028092</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0009904746528898935</v>
+        <v>0.001980949305779787</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0009980626412657411</v>
+        <v>0.001996125282531482</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001005650629641589</v>
+        <v>0.002011301259283178</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001013238618017436</v>
+        <v>0.002026477236034872</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001020826606393284</v>
+        <v>0.002041653212786568</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001028414594769132</v>
+        <v>0.002056829189538264</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001036002583144979</v>
+        <v>0.002072005166289958</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001043590571520827</v>
+        <v>0.002087181143041654</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001051178559896674</v>
+        <v>0.002102357119793348</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001058766548272522</v>
+        <v>0.002117533096545044</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001066354536648369</v>
+        <v>0.002132709073296738</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001073942525024217</v>
+        <v>0.002147885050048434</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001081530513400065</v>
+        <v>0.00216306102680013</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001089118501775912</v>
+        <v>0.002178237003551824</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00109670649015176</v>
+        <v>0.00219341298030352</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001104294478527608</v>
+        <v>0.002208588957055216</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0009601226993865032</v>
+        <v>0.001920245398773006</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009677106877623507</v>
+        <v>0.001935421375524701</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009752986761381984</v>
+        <v>0.001950597352276397</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009828866645140461</v>
+        <v>0.001965773329028092</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0009904746528898935</v>
+        <v>0.001980949305779787</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009980626412657411</v>
+        <v>0.001996125282531482</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001005650629641589</v>
+        <v>0.002011301259283178</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001013238618017436</v>
+        <v>0.002026477236034872</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001020826606393284</v>
+        <v>0.002041653212786568</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001028414594769132</v>
+        <v>0.002056829189538264</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001036002583144979</v>
+        <v>0.002072005166289958</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001043590571520827</v>
+        <v>0.002087181143041654</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001051178559896674</v>
+        <v>0.002102357119793348</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001058766548272522</v>
+        <v>0.002117533096545044</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001066354536648369</v>
+        <v>0.002132709073296738</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001073942525024217</v>
+        <v>0.002147885050048434</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001081530513400065</v>
+        <v>0.00216306102680013</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001089118501775912</v>
+        <v>0.002178237003551824</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00109670649015176</v>
+        <v>0.00219341298030352</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001104294478527608</v>
+        <v>0.002208588957055216</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/73.xlsx
+++ b/BVSimulationFiles/73.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001920245398773006</v>
+        <v>0.01920245398773006</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001935421375524701</v>
+        <v>0.01935421375524701</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001950597352276397</v>
+        <v>0.01950597352276397</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001965773329028092</v>
+        <v>0.01965773329028092</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001980949305779787</v>
+        <v>0.01980949305779787</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001996125282531482</v>
+        <v>0.01996125282531482</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002011301259283178</v>
+        <v>0.02011301259283178</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002026477236034872</v>
+        <v>0.02026477236034872</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002041653212786568</v>
+        <v>0.02041653212786568</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002056829189538264</v>
+        <v>0.02056829189538264</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002072005166289958</v>
+        <v>0.02072005166289958</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002087181143041654</v>
+        <v>0.02087181143041654</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002102357119793348</v>
+        <v>0.02102357119793348</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002117533096545044</v>
+        <v>0.02117533096545044</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002132709073296738</v>
+        <v>0.02132709073296738</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.002147885050048434</v>
+        <v>0.02147885050048434</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00216306102680013</v>
+        <v>0.0216306102680013</v>
       </c>
       <c r="S2" t="n">
-        <v>0.002178237003551824</v>
+        <v>0.02178237003551824</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00219341298030352</v>
+        <v>0.0219341298030352</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002208588957055216</v>
+        <v>0.02208588957055216</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001920245398773006</v>
+        <v>0.01920245398773006</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001935421375524701</v>
+        <v>0.01935421375524701</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001950597352276397</v>
+        <v>0.01950597352276397</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001965773329028092</v>
+        <v>0.01965773329028092</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001980949305779787</v>
+        <v>0.01980949305779787</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001996125282531482</v>
+        <v>0.01996125282531482</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002011301259283178</v>
+        <v>0.02011301259283178</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002026477236034872</v>
+        <v>0.02026477236034872</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002041653212786568</v>
+        <v>0.02041653212786568</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002056829189538264</v>
+        <v>0.02056829189538264</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002072005166289958</v>
+        <v>0.02072005166289958</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002087181143041654</v>
+        <v>0.02087181143041654</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002102357119793348</v>
+        <v>0.02102357119793348</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002117533096545044</v>
+        <v>0.02117533096545044</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002132709073296738</v>
+        <v>0.02132709073296738</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002147885050048434</v>
+        <v>0.02147885050048434</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00216306102680013</v>
+        <v>0.0216306102680013</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002178237003551824</v>
+        <v>0.02178237003551824</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00219341298030352</v>
+        <v>0.0219341298030352</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002208588957055216</v>
+        <v>0.02208588957055216</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/73.xlsx
+++ b/BVSimulationFiles/73.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01920245398773006</v>
+        <v>0.0937474071055803</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01935421375524701</v>
+        <v>0.09448830640505268</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01950597352276397</v>
+        <v>0.09522920570452506</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01965773329028092</v>
+        <v>0.09597010500399746</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01980949305779787</v>
+        <v>0.09671100430346984</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01996125282531482</v>
+        <v>0.09745190360294222</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02011301259283178</v>
+        <v>0.0981928029024146</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02026477236034872</v>
+        <v>0.09893370220188698</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02041653212786568</v>
+        <v>0.09967460150135939</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02056829189538264</v>
+        <v>0.1004155008008318</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02072005166289958</v>
+        <v>0.1011564001003041</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02087181143041654</v>
+        <v>0.1018972993997765</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02102357119793348</v>
+        <v>0.1026381986992489</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02117533096545044</v>
+        <v>0.1033790979987213</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02132709073296738</v>
+        <v>0.1041199972981937</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02147885050048434</v>
+        <v>0.1048608965976661</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0216306102680013</v>
+        <v>0.1056017958971385</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02178237003551824</v>
+        <v>0.1063426951966108</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0219341298030352</v>
+        <v>0.1070835944960832</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02208588957055216</v>
+        <v>0.1078244937955556</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01920245398773006</v>
+        <v>0.0937474071055803</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01935421375524701</v>
+        <v>0.09448830640505268</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01950597352276397</v>
+        <v>0.09522920570452506</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01965773329028092</v>
+        <v>0.09597010500399746</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01980949305779787</v>
+        <v>0.09671100430346984</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01996125282531482</v>
+        <v>0.09745190360294222</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02011301259283178</v>
+        <v>0.0981928029024146</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02026477236034872</v>
+        <v>0.09893370220188698</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02041653212786568</v>
+        <v>0.09967460150135939</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02056829189538264</v>
+        <v>0.1004155008008318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02072005166289958</v>
+        <v>0.1011564001003041</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02087181143041654</v>
+        <v>0.1018972993997765</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02102357119793348</v>
+        <v>0.1026381986992489</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02117533096545044</v>
+        <v>0.1033790979987213</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02132709073296738</v>
+        <v>0.1041199972981937</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02147885050048434</v>
+        <v>0.1048608965976661</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0216306102680013</v>
+        <v>0.1056017958971385</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02178237003551824</v>
+        <v>0.1063426951966108</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0219341298030352</v>
+        <v>0.1070835944960832</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02208588957055216</v>
+        <v>0.1078244937955556</v>
       </c>
     </row>
   </sheetData>
